--- a/docs/StructureDefinition-VAERSImmunization-pvac4.xlsx
+++ b/docs/StructureDefinition-VAERSImmunization-pvac4.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file ADERS (undefined) to us-core-immunization</t>
+    <t>This StructureDefinition contains the maps for ADERS to us-core-immunization</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -237,7 +237,7 @@
     <t>Constraint(s)</t>
   </si>
   <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+    <t>Mapping: VA Adverse Drug Event Reporting System (VA ADERS)</t>
   </si>
   <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
@@ -576,7 +576,7 @@
 </t>
   </si>
   <si>
-    <t>1941: source value from ADERS - 22_PVac4_TypeBrand</t>
+    <t>1941: source value from ADERS - 22_PVac4_TypeBrand (A-22.41)</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -696,7 +696,7 @@
 </t>
   </si>
   <si>
-    <t>1947: source value from ADERS - 22_PVac4_Date</t>
+    <t>1947: source value from ADERS - 22_PVac4_Date (A-22.47)</t>
   </si>
   <si>
     <t>Immunization.recorded</t>
@@ -919,7 +919,7 @@
     <t>Reference.display</t>
   </si>
   <si>
-    <t>1942: source value from ADERS - 22_PVac4_Mfgr</t>
+    <t>1942: source value from ADERS - 22_PVac4_Mfgr (A-22.42)</t>
   </si>
   <si>
     <t>Immunization.lotNumber</t>
@@ -931,7 +931,7 @@
     <t>Lot number of the  vaccine product.</t>
   </si>
   <si>
-    <t>1943: source value from ADERS - 22_PVac4_Lot</t>
+    <t>1943: source value from ADERS - 22_PVac4_Lot (A-22.43)</t>
   </si>
   <si>
     <t>RXA-15</t>
@@ -977,7 +977,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-site</t>
   </si>
   <si>
-    <t>1945: source value from ADERS - 22_PVac4_Site</t>
+    <t>1945: source value from ADERS - 22_PVac4_Site (A-22.45)</t>
   </si>
   <si>
     <t>RXR-2</t>
@@ -1004,7 +1004,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-route</t>
   </si>
   <si>
-    <t>1944: source value from ADERS - 22_PVac4_Route</t>
+    <t>1944: source value from ADERS - 22_PVac4_Route (A-22.44)</t>
   </si>
   <si>
     <t>RXR-1</t>
@@ -1461,7 +1461,7 @@
     <t>doseNumberString</t>
   </si>
   <si>
-    <t>1946: source value from ADERS - 22_PVac4_DoseInSeries</t>
+    <t>1946: source value from ADERS - 22_PVac4_DoseInSeries (A-22.46)</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.seriesDoses[x]</t>
@@ -1825,7 +1825,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="67.44921875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="147.5546875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-VAERSImmunization-pvac4.xlsx
+++ b/docs/StructureDefinition-VAERSImmunization-pvac4.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunization-pvac4.xlsx
+++ b/docs/StructureDefinition-VAERSImmunization-pvac4.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunization-pvac4.xlsx
+++ b/docs/StructureDefinition-VAERSImmunization-pvac4.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2814" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2816" uniqueCount="471">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for ADERS to us-core-immunization</t>
+    <t>This StructureDefinition contains the maps for ADERS to Immunization</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-immunization</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Immunization</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -274,11 +274,11 @@
     <t>Immunization event information</t>
   </si>
   <si>
-    <t>\-</t>
+    <t>Describes the event of a patient being administered a vaccine or a record of an immunization as reported by a patient, a clinician or another party.</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}us-core-5:SHOULD have a translation to the NDC value set {vaccineCode.coding.where(system='http://hl7.org/fhir/sid/ndc').empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -517,7 +517,10 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-status</t>
+    <t>A set of codes indicating the current status of an Immunization.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/immunization-status|4.0.1</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -548,6 +551,9 @@
     <t>example</t>
   </si>
   <si>
+    <t>The reason why a vaccine was not administered.</t>
+  </si>
+  <si>
     <t>http://hl7.org/fhir/ValueSet/immunization-status-reason</t>
   </si>
   <si>
@@ -560,23 +566,19 @@
     <t>Immunization.vaccineCode</t>
   </si>
   <si>
-    <t>Vaccine Product Type (bind to CVX)</t>
+    <t>Vaccine product administered</t>
   </si>
   <si>
     <t>Vaccine that was administered or was to be administered.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1010.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">us-core-5
-</t>
-  </si>
-  <si>
-    <t>1941: source value from ADERS - 22_PVac4_TypeBrand (A-22.41)</t>
+    <t>The code for vaccine product administered.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/vaccine-code</t>
+  </si>
+  <si>
+    <t>1941: source value from ADERS - PVac4_TypeBrand (A-22.41)</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -597,11 +599,7 @@
     <t>Immunization.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Patient
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(Patient)
 </t>
   </si>
   <si>
@@ -696,7 +694,7 @@
 </t>
   </si>
   <si>
-    <t>1947: source value from ADERS - 22_PVac4_Date (A-22.47)</t>
+    <t>1947: source value from ADERS - PVac4_Date (A-22.47)</t>
   </si>
   <si>
     <t>Immunization.recorded</t>
@@ -872,6 +870,9 @@
   </si>
   <si>
     <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
+  </si>
+  <si>
+    <t>extensible</t>
   </si>
   <si>
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
@@ -919,7 +920,7 @@
     <t>Reference.display</t>
   </si>
   <si>
-    <t>1942: source value from ADERS - 22_PVac4_Mfgr (A-22.42)</t>
+    <t>1942: source value from ADERS - PVac4_Mfgr (A-22.42)</t>
   </si>
   <si>
     <t>Immunization.lotNumber</t>
@@ -931,7 +932,7 @@
     <t>Lot number of the  vaccine product.</t>
   </si>
   <si>
-    <t>1943: source value from ADERS - 22_PVac4_Lot (A-22.43)</t>
+    <t>1943: source value from ADERS - PVac4_Lot (A-22.43)</t>
   </si>
   <si>
     <t>RXA-15</t>
@@ -977,7 +978,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-site</t>
   </si>
   <si>
-    <t>1945: source value from ADERS - 22_PVac4_Site (A-22.45)</t>
+    <t>1945: source value from ADERS - PVac4_Site (A-22.45)</t>
   </si>
   <si>
     <t>RXR-2</t>
@@ -1004,7 +1005,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-route</t>
   </si>
   <si>
-    <t>1944: source value from ADERS - 22_PVac4_Route (A-22.44)</t>
+    <t>1944: source value from ADERS - PVac4_Route (A-22.44)</t>
   </si>
   <si>
     <t>RXR-1</t>
@@ -1461,7 +1462,7 @@
     <t>doseNumberString</t>
   </si>
   <si>
-    <t>1946: source value from ADERS - 22_PVac4_DoseInSeries (A-22.46)</t>
+    <t>1946: source value from ADERS - PVac4_DoseInSeries (A-22.46)</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.seriesDoses[x]</t>
@@ -1800,7 +1801,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="67.61328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="50.07421875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1815,7 +1816,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="66.7265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.8515625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.24609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -2001,9 +2002,7 @@
       <c r="M2" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="N2" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
         <v>80</v>
@@ -3212,7 +3211,7 @@
         <v>91</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>92</v>
@@ -3258,9 +3257,11 @@
       <c r="X12" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="Y12" s="2"/>
+      <c r="Y12" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="Z12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>80</v>
@@ -3299,16 +3300,16 @@
         <v>80</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AQ12" t="s" s="2">
         <v>80</v>
@@ -3316,10 +3317,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3333,7 +3334,7 @@
         <v>91</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>80</v>
@@ -3342,16 +3343,16 @@
         <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3377,11 +3378,13 @@
         <v>80</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="Y13" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="Z13" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>80</v>
@@ -3399,7 +3402,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -3420,13 +3423,13 @@
         <v>80</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>80</v>
@@ -3437,10 +3440,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3463,13 +3466,13 @@
         <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3496,11 +3499,13 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y14" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="Z14" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -3518,7 +3523,7 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>91</v>
@@ -3527,43 +3532,43 @@
         <v>91</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>187</v>
+        <v>80</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3573,7 +3578,7 @@
         <v>91</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>80</v>
@@ -3639,7 +3644,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>91</v>
@@ -3815,7 +3820,7 @@
         <v>91</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>80</v>
@@ -4176,13 +4181,13 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>80</v>
@@ -4314,7 +4319,7 @@
         <v>80</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>233</v>
@@ -4349,7 +4354,7 @@
         <v>80</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y21" t="s" s="2">
         <v>236</v>
@@ -5081,13 +5086,13 @@
         <v>80</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>177</v>
+        <v>275</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>80</v>
@@ -5105,7 +5110,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5143,10 +5148,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5172,13 +5177,13 @@
         <v>149</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5228,7 +5233,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5255,7 +5260,7 @@
         <v>80</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>80</v>
@@ -5266,10 +5271,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5295,13 +5300,13 @@
         <v>255</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5351,7 +5356,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5366,7 +5371,7 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>80</v>
@@ -5389,10 +5394,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5418,10 +5423,10 @@
         <v>255</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5472,7 +5477,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5487,7 +5492,7 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>80</v>
@@ -5496,24 +5501,24 @@
         <v>80</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5536,13 +5541,13 @@
         <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5593,7 +5598,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5617,10 +5622,10 @@
         <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>80</v>
@@ -5631,10 +5636,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5657,13 +5662,13 @@
         <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5690,13 +5695,13 @@
         <v>80</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>80</v>
@@ -5714,7 +5719,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5729,7 +5734,7 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>80</v>
@@ -5738,24 +5743,24 @@
         <v>80</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5778,13 +5783,13 @@
         <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5811,13 +5816,13 @@
         <v>80</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>80</v>
@@ -5835,7 +5840,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5850,7 +5855,7 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>80</v>
@@ -5859,24 +5864,24 @@
         <v>80</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5899,13 +5904,13 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5956,7 +5961,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -5980,10 +5985,10 @@
         <v>80</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>80</v>
@@ -5994,10 +5999,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6020,13 +6025,13 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6077,7 +6082,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6098,13 +6103,13 @@
         <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>80</v>
@@ -6115,10 +6120,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6236,10 +6241,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6359,14 +6364,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6388,10 +6393,10 @@
         <v>137</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>140</v>
@@ -6446,7 +6451,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6484,10 +6489,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6510,13 +6515,13 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6543,13 +6548,13 @@
         <v>80</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>177</v>
+        <v>275</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>80</v>
@@ -6567,7 +6572,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6588,13 +6593,13 @@
         <v>80</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>80</v>
@@ -6605,10 +6610,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6631,16 +6636,16 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6690,7 +6695,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>91</v>
@@ -6711,16 +6716,16 @@
         <v>80</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>80</v>
@@ -6728,10 +6733,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6754,13 +6759,13 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6811,7 +6816,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6832,13 +6837,13 @@
         <v>80</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>80</v>
@@ -6849,10 +6854,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6875,13 +6880,13 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6908,13 +6913,13 @@
         <v>80</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>80</v>
@@ -6932,7 +6937,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -6953,13 +6958,13 @@
         <v>80</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>80</v>
@@ -6970,10 +6975,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6996,13 +7001,13 @@
         <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7053,7 +7058,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7074,7 +7079,7 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>80</v>
@@ -7091,10 +7096,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7120,20 +7125,20 @@
         <v>225</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q44" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="R44" t="s" s="2">
         <v>80</v>
@@ -7178,7 +7183,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7202,7 +7207,7 @@
         <v>80</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>134</v>
@@ -7216,10 +7221,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7242,13 +7247,13 @@
         <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7275,13 +7280,13 @@
         <v>80</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>80</v>
@@ -7299,7 +7304,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7337,10 +7342,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7363,13 +7368,13 @@
         <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7420,7 +7425,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7432,7 +7437,7 @@
         <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>80</v>
@@ -7458,10 +7463,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7579,10 +7584,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7702,14 +7707,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7731,10 +7736,10 @@
         <v>137</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>140</v>
@@ -7789,7 +7794,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7827,10 +7832,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7856,10 +7861,10 @@
         <v>255</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7910,7 +7915,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7934,7 +7939,7 @@
         <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>134</v>
@@ -7948,10 +7953,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7977,10 +7982,10 @@
         <v>105</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8031,7 +8036,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8069,10 +8074,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8098,10 +8103,10 @@
         <v>217</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8152,7 +8157,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8176,7 +8181,7 @@
         <v>80</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>134</v>
@@ -8190,10 +8195,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8219,10 +8224,10 @@
         <v>217</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8273,7 +8278,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8297,7 +8302,7 @@
         <v>80</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>134</v>
@@ -8311,10 +8316,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8337,13 +8342,13 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8370,13 +8375,13 @@
         <v>80</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>80</v>
@@ -8394,7 +8399,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8418,7 +8423,7 @@
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>134</v>
@@ -8432,10 +8437,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8458,13 +8463,13 @@
         <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8491,13 +8496,13 @@
         <v>80</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>80</v>
@@ -8515,7 +8520,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8553,10 +8558,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8579,16 +8584,16 @@
         <v>80</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8638,7 +8643,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8662,10 +8667,10 @@
         <v>80</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>80</v>
@@ -8676,10 +8681,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8797,10 +8802,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8920,14 +8925,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8949,10 +8954,10 @@
         <v>137</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>140</v>
@@ -9007,7 +9012,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9045,10 +9050,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9074,10 +9079,10 @@
         <v>217</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9128,7 +9133,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9152,7 +9157,7 @@
         <v>80</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>212</v>
@@ -9166,10 +9171,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9192,13 +9197,13 @@
         <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9249,7 +9254,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9273,10 +9278,10 @@
         <v>80</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>80</v>
@@ -9287,10 +9292,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9316,10 +9321,10 @@
         <v>225</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9370,7 +9375,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9394,10 +9399,10 @@
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>80</v>
@@ -9408,10 +9413,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9434,13 +9439,13 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9491,7 +9496,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9529,10 +9534,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9650,10 +9655,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9773,14 +9778,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9802,10 +9807,10 @@
         <v>137</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>140</v>
@@ -9860,7 +9865,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -9898,10 +9903,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9927,10 +9932,10 @@
         <v>255</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9981,7 +9986,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10019,10 +10024,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10048,10 +10053,10 @@
         <v>248</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10102,7 +10107,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10140,10 +10145,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10166,13 +10171,13 @@
         <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10199,13 +10204,13 @@
         <v>80</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>80</v>
@@ -10223,7 +10228,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10261,10 +10266,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10287,16 +10292,16 @@
         <v>80</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10344,7 +10349,7 @@
         <v>209</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>91</v>
@@ -10382,13 +10387,13 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>80</v>
@@ -10413,13 +10418,13 @@
         <v>255</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10469,7 +10474,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>91</v>
@@ -10484,7 +10489,7 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>80</v>
@@ -10507,10 +10512,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10533,16 +10538,16 @@
         <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10592,7 +10597,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-VAERSImmunization-pvac4.xlsx
+++ b/docs/StructureDefinition-VAERSImmunization-pvac4.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2816" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2814" uniqueCount="470">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for ADERS to Immunization</t>
+    <t>This StructureDefinition contains the maps for ADERS to us-core-immunization</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Immunization</t>
+    <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-immunization</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -274,11 +274,11 @@
     <t>Immunization event information</t>
   </si>
   <si>
-    <t>Describes the event of a patient being administered a vaccine or a record of an immunization as reported by a patient, a clinician or another party.</t>
+    <t>\-</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}us-core-5:SHOULD have a translation to the NDC value set {vaccineCode.coding.where(system='http://hl7.org/fhir/sid/ndc').empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -517,10 +517,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>A set of codes indicating the current status of an Immunization.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-status|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-status</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -551,9 +548,6 @@
     <t>example</t>
   </si>
   <si>
-    <t>The reason why a vaccine was not administered.</t>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/ValueSet/immunization-status-reason</t>
   </si>
   <si>
@@ -566,19 +560,23 @@
     <t>Immunization.vaccineCode</t>
   </si>
   <si>
-    <t>Vaccine product administered</t>
+    <t>Vaccine Product Type (bind to CVX)</t>
   </si>
   <si>
     <t>Vaccine that was administered or was to be administered.</t>
   </si>
   <si>
-    <t>The code for vaccine product administered.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/vaccine-code</t>
-  </si>
-  <si>
-    <t>1941: source value from ADERS - PVac4_TypeBrand (A-22.41)</t>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1010.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">us-core-5
+</t>
+  </si>
+  <si>
+    <t>1941: source value from ADERS - 22_PVac4_TypeBrand</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -599,7 +597,11 @@
     <t>Immunization.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient)
+    <t xml:space="preserve">Patient
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
 </t>
   </si>
   <si>
@@ -694,7 +696,7 @@
 </t>
   </si>
   <si>
-    <t>1947: source value from ADERS - PVac4_Date (A-22.47)</t>
+    <t>1947: source value from ADERS - 22_PVac4_Date</t>
   </si>
   <si>
     <t>Immunization.recorded</t>
@@ -870,9 +872,6 @@
   </si>
   <si>
     <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
@@ -920,7 +919,7 @@
     <t>Reference.display</t>
   </si>
   <si>
-    <t>1942: source value from ADERS - PVac4_Mfgr (A-22.42)</t>
+    <t>1942: source value from ADERS - 22_PVac4_Mfgr</t>
   </si>
   <si>
     <t>Immunization.lotNumber</t>
@@ -932,7 +931,7 @@
     <t>Lot number of the  vaccine product.</t>
   </si>
   <si>
-    <t>1943: source value from ADERS - PVac4_Lot (A-22.43)</t>
+    <t>1943: source value from ADERS - 22_PVac4_Lot</t>
   </si>
   <si>
     <t>RXA-15</t>
@@ -978,7 +977,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-site</t>
   </si>
   <si>
-    <t>1945: source value from ADERS - PVac4_Site (A-22.45)</t>
+    <t>1945: source value from ADERS - 22_PVac4_Site</t>
   </si>
   <si>
     <t>RXR-2</t>
@@ -1005,7 +1004,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-route</t>
   </si>
   <si>
-    <t>1944: source value from ADERS - PVac4_Route (A-22.44)</t>
+    <t>1944: source value from ADERS - 22_PVac4_Route</t>
   </si>
   <si>
     <t>RXR-1</t>
@@ -1462,7 +1461,7 @@
     <t>doseNumberString</t>
   </si>
   <si>
-    <t>1946: source value from ADERS - PVac4_DoseInSeries (A-22.46)</t>
+    <t>1946: source value from ADERS - 22_PVac4_DoseInSeries</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.seriesDoses[x]</t>
@@ -1801,7 +1800,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="50.07421875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="67.61328125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1816,7 +1815,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="66.7265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="56.24609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.8515625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -2002,7 +2001,9 @@
       <c r="M2" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="N2" s="2"/>
+      <c r="N2" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
         <v>80</v>
@@ -3211,7 +3212,7 @@
         <v>91</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>92</v>
@@ -3257,11 +3258,9 @@
       <c r="X12" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="Y12" t="s" s="2">
+      <c r="Y12" s="2"/>
+      <c r="Z12" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>80</v>
@@ -3300,16 +3299,16 @@
         <v>80</v>
       </c>
       <c r="AM12" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AN12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO12" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="AN12" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO12" t="s" s="2">
+      <c r="AP12" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AP12" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="AQ12" t="s" s="2">
         <v>80</v>
@@ -3317,10 +3316,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3334,7 +3333,7 @@
         <v>91</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>80</v>
@@ -3343,16 +3342,16 @@
         <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3378,14 +3377,12 @@
         <v>80</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Y13" s="2"/>
+      <c r="Z13" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="Y13" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>173</v>
-      </c>
       <c r="AA13" t="s" s="2">
         <v>80</v>
       </c>
@@ -3402,7 +3399,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -3423,13 +3420,13 @@
         <v>80</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>80</v>
@@ -3440,10 +3437,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3466,13 +3463,13 @@
         <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3499,76 +3496,74 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="Y14" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="Y14" s="2"/>
+      <c r="Z14" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI14" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="AL14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="AO14" t="s" s="2">
+      <c r="AP14" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="AP14" t="s" s="2">
+      <c r="AQ14" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AQ14" t="s" s="2">
-        <v>186</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>80</v>
+        <v>187</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3578,7 +3573,7 @@
         <v>91</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>80</v>
@@ -3644,7 +3639,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>91</v>
@@ -3820,7 +3815,7 @@
         <v>91</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>80</v>
@@ -4181,13 +4176,13 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>80</v>
@@ -4319,7 +4314,7 @@
         <v>80</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>233</v>
@@ -4354,7 +4349,7 @@
         <v>80</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y21" t="s" s="2">
         <v>236</v>
@@ -5086,31 +5081,31 @@
         <v>80</v>
       </c>
       <c r="X27" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="Y27" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="Y27" t="s" s="2">
+      <c r="Z27" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="Z27" t="s" s="2">
+      <c r="AA27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5148,10 +5143,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5177,13 +5172,13 @@
         <v>149</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5233,7 +5228,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5260,7 +5255,7 @@
         <v>80</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>80</v>
@@ -5271,10 +5266,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5300,13 +5295,13 @@
         <v>255</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5356,7 +5351,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5371,7 +5366,7 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>80</v>
@@ -5394,10 +5389,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5423,10 +5418,10 @@
         <v>255</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5477,7 +5472,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5492,33 +5487,33 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AL30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="AO30" t="s" s="2">
+      <c r="AP30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ30" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ30" t="s" s="2">
-        <v>297</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5541,13 +5536,13 @@
         <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5598,7 +5593,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5622,10 +5617,10 @@
         <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>80</v>
@@ -5636,10 +5631,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5662,13 +5657,13 @@
         <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5695,14 +5690,14 @@
         <v>80</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y32" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="Z32" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="Z32" t="s" s="2">
-        <v>308</v>
-      </c>
       <c r="AA32" t="s" s="2">
         <v>80</v>
       </c>
@@ -5719,7 +5714,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5734,33 +5729,33 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AL32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AO32" t="s" s="2">
+      <c r="AP32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ32" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ32" t="s" s="2">
-        <v>312</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5783,13 +5778,13 @@
         <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5816,14 +5811,14 @@
         <v>80</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y33" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="Z33" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="Z33" t="s" s="2">
-        <v>317</v>
-      </c>
       <c r="AA33" t="s" s="2">
         <v>80</v>
       </c>
@@ -5840,7 +5835,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5855,33 +5850,33 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AL33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="AO33" t="s" s="2">
+      <c r="AP33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ33" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ33" t="s" s="2">
-        <v>321</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5904,13 +5899,13 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5961,7 +5956,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -5985,10 +5980,10 @@
         <v>80</v>
       </c>
       <c r="AN34" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>80</v>
@@ -5999,10 +5994,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6025,13 +6020,13 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6082,7 +6077,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6103,13 +6098,13 @@
         <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>80</v>
@@ -6120,10 +6115,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6241,10 +6236,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6364,14 +6359,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6393,10 +6388,10 @@
         <v>137</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>140</v>
@@ -6451,7 +6446,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6489,10 +6484,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6515,13 +6510,13 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6548,14 +6543,14 @@
         <v>80</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>275</v>
+        <v>177</v>
       </c>
       <c r="Y39" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="Z39" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>346</v>
-      </c>
       <c r="AA39" t="s" s="2">
         <v>80</v>
       </c>
@@ -6572,7 +6567,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6593,13 +6588,13 @@
         <v>80</v>
       </c>
       <c r="AM39" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO39" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>80</v>
@@ -6610,10 +6605,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6636,16 +6631,16 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6695,7 +6690,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>91</v>
@@ -6716,16 +6711,16 @@
         <v>80</v>
       </c>
       <c r="AM40" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO40" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AN40" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO40" t="s" s="2">
+      <c r="AP40" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>80</v>
@@ -6733,10 +6728,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6759,13 +6754,13 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6816,7 +6811,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6837,13 +6832,13 @@
         <v>80</v>
       </c>
       <c r="AM41" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>80</v>
@@ -6854,10 +6849,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6880,13 +6875,13 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6913,14 +6908,14 @@
         <v>80</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y42" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="Z42" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="Z42" t="s" s="2">
-        <v>368</v>
-      </c>
       <c r="AA42" t="s" s="2">
         <v>80</v>
       </c>
@@ -6937,7 +6932,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -6958,13 +6953,13 @@
         <v>80</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>80</v>
@@ -6975,10 +6970,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7001,13 +6996,13 @@
         <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7058,7 +7053,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7079,7 +7074,7 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>80</v>
@@ -7096,10 +7091,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7125,20 +7120,20 @@
         <v>225</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q44" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="R44" t="s" s="2">
         <v>80</v>
@@ -7183,7 +7178,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7207,7 +7202,7 @@
         <v>80</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>134</v>
@@ -7221,10 +7216,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7247,13 +7242,13 @@
         <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7280,14 +7275,14 @@
         <v>80</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="Z45" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="Z45" t="s" s="2">
-        <v>385</v>
-      </c>
       <c r="AA45" t="s" s="2">
         <v>80</v>
       </c>
@@ -7304,7 +7299,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7342,10 +7337,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7368,13 +7363,13 @@
         <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7425,7 +7420,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7437,7 +7432,7 @@
         <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>80</v>
@@ -7463,10 +7458,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7584,10 +7579,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7707,14 +7702,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7736,10 +7731,10 @@
         <v>137</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>140</v>
@@ -7794,7 +7789,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7832,10 +7827,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7861,10 +7856,10 @@
         <v>255</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7915,7 +7910,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7939,7 +7934,7 @@
         <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>134</v>
@@ -7953,10 +7948,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7982,10 +7977,10 @@
         <v>105</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8036,7 +8031,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8074,10 +8069,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8103,10 +8098,10 @@
         <v>217</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8157,7 +8152,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8181,7 +8176,7 @@
         <v>80</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>134</v>
@@ -8195,10 +8190,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8224,10 +8219,10 @@
         <v>217</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8278,7 +8273,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8302,7 +8297,7 @@
         <v>80</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>134</v>
@@ -8316,10 +8311,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8342,13 +8337,13 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8375,14 +8370,14 @@
         <v>80</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y54" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="Z54" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="Z54" t="s" s="2">
-        <v>412</v>
-      </c>
       <c r="AA54" t="s" s="2">
         <v>80</v>
       </c>
@@ -8399,7 +8394,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8423,7 +8418,7 @@
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>134</v>
@@ -8437,10 +8432,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8463,13 +8458,13 @@
         <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8496,14 +8491,14 @@
         <v>80</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y55" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="Z55" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="Z55" t="s" s="2">
-        <v>418</v>
-      </c>
       <c r="AA55" t="s" s="2">
         <v>80</v>
       </c>
@@ -8520,7 +8515,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8558,10 +8553,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8584,16 +8579,16 @@
         <v>80</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8643,7 +8638,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8667,10 +8662,10 @@
         <v>80</v>
       </c>
       <c r="AN56" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AO56" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>80</v>
@@ -8681,10 +8676,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8802,10 +8797,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8925,14 +8920,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8954,10 +8949,10 @@
         <v>137</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>140</v>
@@ -9012,7 +9007,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9050,10 +9045,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9079,10 +9074,10 @@
         <v>217</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9133,7 +9128,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9157,7 +9152,7 @@
         <v>80</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>212</v>
@@ -9171,10 +9166,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9197,13 +9192,13 @@
         <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9254,7 +9249,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9278,10 +9273,10 @@
         <v>80</v>
       </c>
       <c r="AN61" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AO61" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>80</v>
@@ -9292,10 +9287,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9321,10 +9316,10 @@
         <v>225</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9375,7 +9370,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9399,10 +9394,10 @@
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AO62" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>80</v>
@@ -9413,10 +9408,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9439,13 +9434,13 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9496,7 +9491,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9534,10 +9529,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9655,10 +9650,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9778,14 +9773,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9807,10 +9802,10 @@
         <v>137</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>140</v>
@@ -9865,7 +9860,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -9903,10 +9898,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9932,10 +9927,10 @@
         <v>255</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9986,7 +9981,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10024,10 +10019,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10053,10 +10048,10 @@
         <v>248</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10107,7 +10102,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10145,10 +10140,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10171,13 +10166,13 @@
         <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10204,14 +10199,14 @@
         <v>80</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y69" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="Z69" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="Z69" t="s" s="2">
-        <v>459</v>
-      </c>
       <c r="AA69" t="s" s="2">
         <v>80</v>
       </c>
@@ -10228,7 +10223,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10266,10 +10261,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10292,16 +10287,16 @@
         <v>80</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10349,7 +10344,7 @@
         <v>209</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>91</v>
@@ -10387,13 +10382,13 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="C71" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="C71" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>80</v>
@@ -10418,13 +10413,13 @@
         <v>255</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10474,7 +10469,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>91</v>
@@ -10489,7 +10484,7 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>80</v>
@@ -10512,10 +10507,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10538,16 +10533,16 @@
         <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="M72" t="s" s="2">
-        <v>470</v>
-      </c>
       <c r="N72" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10597,7 +10592,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-VAERSImmunization-pvac4.xlsx
+++ b/docs/StructureDefinition-VAERSImmunization-pvac4.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
